--- a/DATA/A077970_valuation_exog.xlsx
+++ b/DATA/A077970_valuation_exog.xlsx
@@ -396,45 +396,45 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>201396855.87683</v>
+        <v>202028093.1019482</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>195927643.631627</v>
+        <v>196247202.7074325</v>
       </c>
       <c r="B3">
-        <v>1.669440433507671</v>
+        <v>1.686986173033195</v>
       </c>
       <c r="C3">
-        <v>327089530.3205199</v>
+        <v>331066317.4638812</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>241644218.7519742</v>
+        <v>242927204.2853888</v>
       </c>
       <c r="B4">
-        <v>1.471013073231239</v>
+        <v>1.479895471296482</v>
       </c>
       <c r="C4">
-        <v>355461804.8549034</v>
+        <v>359506869.4766623</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>160399805.16868</v>
+        <v>161371285.3192832</v>
       </c>
       <c r="B5">
-        <v>1.842908423786017</v>
+        <v>1.878570024668459</v>
       </c>
       <c r="C5">
-        <v>295602152.1189961</v>
+        <v>303147259.4430268</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="B6">
-        <v>1.82326406420254</v>
+        <v>1.850267125806692</v>
       </c>
     </row>
   </sheetData>
